--- a/RAMON FRANCO/Mayo/GASTOS_RAMON FRANCO_MAYO.xlsx
+++ b/RAMON FRANCO/Mayo/GASTOS_RAMON FRANCO_MAYO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\RAMON FRANCO\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF9D361-70F6-4424-A1CF-93FD4DA8CB61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA11FFD6-574A-487D-8B59-665CA2E75486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$70</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$71</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -184,6 +184,9 @@
   </si>
   <si>
     <t>PERIODO: MAYO - Vto. 16/06</t>
+  </si>
+  <si>
+    <t>Salvatierra Matias - Desobstruccion 3B</t>
   </si>
 </sst>
 </file>
@@ -485,7 +488,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -580,6 +583,8 @@
     </xf>
     <xf numFmtId="44" fontId="8" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="7" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="12" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="12" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -664,8 +669,7 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="12" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="12" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="12" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -1003,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
@@ -1038,10 +1042,10 @@
       <c r="D3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="73">
+      <c r="E3" s="75">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="73"/>
+      <c r="F3" s="75"/>
       <c r="H3" s="6"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -1118,16 +1122,16 @@
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="83" t="s">
+      <c r="A12" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="83"/>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
+      <c r="B12" s="85"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="85"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="85"/>
+      <c r="H12" s="85"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="18"/>
@@ -1167,7 +1171,7 @@
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
-      <c r="H15" s="99">
+      <c r="H15" s="71">
         <v>8379</v>
       </c>
     </row>
@@ -1207,16 +1211,16 @@
       <c r="H18" s="52"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="84" t="s">
+      <c r="A19" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="85"/>
-      <c r="C19" s="85"/>
-      <c r="D19" s="85"/>
-      <c r="E19" s="85"/>
-      <c r="F19" s="85"/>
-      <c r="G19" s="85"/>
-      <c r="H19" s="86"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="87"/>
+      <c r="G19" s="87"/>
+      <c r="H19" s="88"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
@@ -1228,7 +1232,7 @@
       <c r="E20" s="19"/>
       <c r="F20" s="19"/>
       <c r="G20" s="19"/>
-      <c r="H20" s="98">
+      <c r="H20" s="70">
         <v>24151.63</v>
       </c>
     </row>
@@ -1258,16 +1262,16 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="84" t="s">
+      <c r="A23" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="85"/>
-      <c r="C23" s="85"/>
-      <c r="D23" s="85"/>
-      <c r="E23" s="85"/>
-      <c r="F23" s="85"/>
-      <c r="G23" s="85"/>
-      <c r="H23" s="86"/>
+      <c r="B23" s="87"/>
+      <c r="C23" s="87"/>
+      <c r="D23" s="87"/>
+      <c r="E23" s="87"/>
+      <c r="F23" s="87"/>
+      <c r="G23" s="87"/>
+      <c r="H23" s="88"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="28" t="s">
@@ -1309,16 +1313,16 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="87" t="s">
+      <c r="A27" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="87"/>
-      <c r="C27" s="87"/>
-      <c r="D27" s="87"/>
-      <c r="E27" s="87"/>
-      <c r="F27" s="87"/>
-      <c r="G27" s="87"/>
-      <c r="H27" s="87"/>
+      <c r="B27" s="89"/>
+      <c r="C27" s="89"/>
+      <c r="D27" s="89"/>
+      <c r="E27" s="89"/>
+      <c r="F27" s="89"/>
+      <c r="G27" s="89"/>
+      <c r="H27" s="89"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
@@ -1351,367 +1355,369 @@
         <v>89897</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="70" t="s">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="100">
+        <v>18500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="71"/>
-      <c r="C30" s="71"/>
-      <c r="D30" s="71"/>
-      <c r="E30" s="71"/>
-      <c r="F30" s="71"/>
-      <c r="G30" s="71"/>
-      <c r="H30" s="26">
+      <c r="B31" s="73"/>
+      <c r="C31" s="73"/>
+      <c r="D31" s="73"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="73"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="26">
         <v>195000</v>
       </c>
-      <c r="K30" s="53"/>
-      <c r="L30" t="s">
+      <c r="K31" s="53"/>
+      <c r="L31" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="21" t="s">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="27">
-        <f>SUM(H28:H30)</f>
-        <v>327730.94</v>
-      </c>
-      <c r="L31" t="s">
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="27">
+        <f>SUM(H28:H31)</f>
+        <v>346230.94</v>
+      </c>
+      <c r="L32" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="84" t="s">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="85"/>
-      <c r="C32" s="85"/>
-      <c r="D32" s="85"/>
-      <c r="E32" s="85"/>
-      <c r="F32" s="85"/>
-      <c r="G32" s="85"/>
-      <c r="H32" s="86"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="18" t="s">
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="87"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="87"/>
+      <c r="H33" s="88"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19" t="s">
+      <c r="B34" s="19"/>
+      <c r="C34" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="53"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A34" s="21" t="s">
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="53"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="68">
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="68">
         <v>134182.76</v>
       </c>
-      <c r="I34" s="53"/>
-      <c r="K34" t="s">
+      <c r="I35" s="53"/>
+      <c r="K35" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="18"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="32"/>
-    </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" s="84" t="s">
+      <c r="A36" s="18"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="32"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" s="86" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="85"/>
-      <c r="C36" s="85"/>
-      <c r="D36" s="85"/>
-      <c r="E36" s="85"/>
-      <c r="F36" s="85"/>
-      <c r="G36" s="85"/>
-      <c r="H36" s="86"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="60" t="s">
+      <c r="B37" s="87"/>
+      <c r="C37" s="87"/>
+      <c r="D37" s="87"/>
+      <c r="E37" s="87"/>
+      <c r="F37" s="87"/>
+      <c r="G37" s="87"/>
+      <c r="H37" s="88"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="61"/>
-      <c r="C37" s="61"/>
-      <c r="D37" s="61"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="61"/>
-      <c r="G37" s="61"/>
-      <c r="H37" s="69">
+      <c r="B38" s="61"/>
+      <c r="C38" s="61"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="61"/>
+      <c r="F38" s="61"/>
+      <c r="G38" s="61"/>
+      <c r="H38" s="69">
         <v>47532.32</v>
       </c>
     </row>
-    <row r="38" spans="1:11" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="33" t="s">
+    <row r="39" spans="1:11" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B38" s="34"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="35">
-        <f>H17+H22+H26+H31+H34+H37</f>
-        <v>795396.65</v>
-      </c>
-      <c r="I38" s="62"/>
-    </row>
-    <row r="39" spans="1:11" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A39" s="55" t="s">
+      <c r="B39" s="34"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="35">
+        <f>H17+H22+H26+H32+H35+H38</f>
+        <v>813896.65</v>
+      </c>
+      <c r="I39" s="62"/>
+    </row>
+    <row r="40" spans="1:11" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A40" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="56"/>
-      <c r="C39" s="56"/>
-      <c r="D39" s="56"/>
-      <c r="E39" s="56"/>
-      <c r="F39" s="56"/>
-      <c r="G39" s="56"/>
-      <c r="H39" s="57"/>
-    </row>
-    <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="74" t="s">
+      <c r="B40" s="56"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="57"/>
+    </row>
+    <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="B40" s="75"/>
-      <c r="C40" s="75"/>
-      <c r="D40" s="75"/>
-      <c r="E40" s="75"/>
-      <c r="F40" s="75"/>
-      <c r="G40" s="75"/>
-      <c r="H40" s="76"/>
-    </row>
-    <row r="41" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="77"/>
-      <c r="B41" s="78"/>
-      <c r="C41" s="78"/>
-      <c r="D41" s="78"/>
-      <c r="E41" s="78"/>
-      <c r="F41" s="78"/>
-      <c r="G41" s="78"/>
-      <c r="H41" s="79"/>
-    </row>
-    <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="88"/>
-      <c r="B42" s="89"/>
-      <c r="C42" s="89"/>
-      <c r="D42" s="89"/>
-      <c r="E42" s="89"/>
-      <c r="F42" s="89"/>
-      <c r="G42" s="90"/>
-      <c r="H42" s="36"/>
-    </row>
-    <row r="43" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="88"/>
-      <c r="B43" s="89"/>
-      <c r="C43" s="89"/>
-      <c r="D43" s="89"/>
-      <c r="E43" s="89"/>
-      <c r="F43" s="89"/>
-      <c r="G43" s="90"/>
+      <c r="B41" s="77"/>
+      <c r="C41" s="77"/>
+      <c r="D41" s="77"/>
+      <c r="E41" s="77"/>
+      <c r="F41" s="77"/>
+      <c r="G41" s="77"/>
+      <c r="H41" s="78"/>
+    </row>
+    <row r="42" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="79"/>
+      <c r="B42" s="80"/>
+      <c r="C42" s="80"/>
+      <c r="D42" s="80"/>
+      <c r="E42" s="80"/>
+      <c r="F42" s="80"/>
+      <c r="G42" s="80"/>
+      <c r="H42" s="81"/>
+    </row>
+    <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="90"/>
+      <c r="B43" s="91"/>
+      <c r="C43" s="91"/>
+      <c r="D43" s="91"/>
+      <c r="E43" s="91"/>
+      <c r="F43" s="91"/>
+      <c r="G43" s="92"/>
       <c r="H43" s="36"/>
     </row>
-    <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="91"/>
-      <c r="B44" s="92"/>
-      <c r="C44" s="92"/>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
-      <c r="F44" s="92"/>
-      <c r="G44" s="93"/>
+    <row r="44" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="90"/>
+      <c r="B44" s="91"/>
+      <c r="C44" s="91"/>
+      <c r="D44" s="91"/>
+      <c r="E44" s="91"/>
+      <c r="F44" s="91"/>
+      <c r="G44" s="92"/>
       <c r="H44" s="36"/>
     </row>
-    <row r="45" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="94" t="s">
+    <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="93"/>
+      <c r="B45" s="94"/>
+      <c r="C45" s="94"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
+      <c r="F45" s="94"/>
+      <c r="G45" s="95"/>
+      <c r="H45" s="36"/>
+    </row>
+    <row r="46" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="96" t="s">
         <v>29</v>
       </c>
-      <c r="B45" s="95"/>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
-      <c r="F45" s="95"/>
-      <c r="G45" s="96"/>
-      <c r="H45" s="37">
-        <f>SUM(H42:H44)</f>
+      <c r="B46" s="97"/>
+      <c r="C46" s="97"/>
+      <c r="D46" s="97"/>
+      <c r="E46" s="97"/>
+      <c r="F46" s="97"/>
+      <c r="G46" s="98"/>
+      <c r="H46" s="37">
+        <f>SUM(H43:H45)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A46" s="19"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-    </row>
-    <row r="47" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="65" t="s">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" s="19"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="19"/>
+    </row>
+    <row r="48" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="B47" s="66"/>
-      <c r="C47" s="66"/>
-      <c r="D47" s="66"/>
-      <c r="E47" s="66"/>
-      <c r="F47" s="66"/>
-      <c r="G47" s="67"/>
-      <c r="H47" s="64">
+      <c r="B48" s="66"/>
+      <c r="C48" s="66"/>
+      <c r="D48" s="66"/>
+      <c r="E48" s="66"/>
+      <c r="F48" s="66"/>
+      <c r="G48" s="67"/>
+      <c r="H48" s="64">
         <v>500000</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="19"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="19"/>
-      <c r="J48" s="15"/>
-    </row>
-    <row r="49" spans="1:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="97" t="s">
+    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="19"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19"/>
+      <c r="J49" s="15"/>
+    </row>
+    <row r="50" spans="1:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="97"/>
-      <c r="C49" s="97"/>
-      <c r="D49" s="97"/>
-      <c r="E49" s="97"/>
-      <c r="F49" s="97"/>
-      <c r="G49" s="97"/>
-      <c r="H49" s="35">
-        <f>+H38+H39</f>
-        <v>795396.65</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="38"/>
-      <c r="B50" s="38"/>
-      <c r="C50" s="38"/>
-      <c r="D50" s="38"/>
-      <c r="E50" s="38"/>
-      <c r="F50" s="38"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="39"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="19"/>
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="19"/>
-    </row>
-    <row r="52" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="33" t="s">
+      <c r="B50" s="99"/>
+      <c r="C50" s="99"/>
+      <c r="D50" s="99"/>
+      <c r="E50" s="99"/>
+      <c r="F50" s="99"/>
+      <c r="G50" s="99"/>
+      <c r="H50" s="35">
+        <f>+H39+H40</f>
+        <v>813896.65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="38"/>
+      <c r="B51" s="38"/>
+      <c r="C51" s="38"/>
+      <c r="D51" s="38"/>
+      <c r="E51" s="38"/>
+      <c r="F51" s="38"/>
+      <c r="G51" s="38"/>
+      <c r="H51" s="39"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="19"/>
+      <c r="B52" s="19"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="19"/>
+    </row>
+    <row r="53" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="B52" s="34"/>
-      <c r="C52" s="34"/>
-      <c r="D52" s="34"/>
-      <c r="E52" s="34"/>
-      <c r="F52" s="34"/>
-      <c r="G52" s="34"/>
-      <c r="H52" s="40">
-        <f>H45</f>
+      <c r="B53" s="34"/>
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="34"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="40">
+        <f>H46</f>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="19"/>
-      <c r="B53" s="19"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="19"/>
-      <c r="E53" s="19"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="19"/>
-    </row>
-    <row r="54" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A54" s="80" t="s">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" s="19"/>
+      <c r="B54" s="19"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="19"/>
+    </row>
+    <row r="55" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="A55" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="B54" s="81"/>
-      <c r="C54" s="81"/>
-      <c r="D54" s="81"/>
-      <c r="E54" s="81"/>
-      <c r="F54" s="81"/>
-      <c r="G54" s="81"/>
-      <c r="H54" s="82"/>
-    </row>
-    <row r="55" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A55" s="41" t="s">
+      <c r="B55" s="83"/>
+      <c r="C55" s="83"/>
+      <c r="D55" s="83"/>
+      <c r="E55" s="83"/>
+      <c r="F55" s="83"/>
+      <c r="G55" s="83"/>
+      <c r="H55" s="84"/>
+    </row>
+    <row r="56" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="A56" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="B55" s="42"/>
-      <c r="C55" s="42"/>
-      <c r="D55" s="42"/>
-      <c r="E55" s="42"/>
-      <c r="F55" s="42"/>
-      <c r="G55" s="42"/>
-      <c r="H55" s="48">
+      <c r="B56" s="42"/>
+      <c r="C56" s="42"/>
+      <c r="D56" s="42"/>
+      <c r="E56" s="42"/>
+      <c r="F56" s="42"/>
+      <c r="G56" s="42"/>
+      <c r="H56" s="48">
         <v>511718.6</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="43" t="s">
+    <row r="57" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="B56" s="44"/>
-      <c r="C56" s="44"/>
-      <c r="D56" s="44"/>
-      <c r="E56" s="44"/>
-      <c r="F56" s="44"/>
-      <c r="G56" s="44"/>
-      <c r="H56" s="54">
-        <v>879633.26716047991</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="43"/>
       <c r="B57" s="44"/>
       <c r="C57" s="44"/>
       <c r="D57" s="44"/>
       <c r="E57" s="44"/>
       <c r="F57" s="44"/>
       <c r="G57" s="44"/>
-      <c r="H57" s="49"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="43" t="s">
-        <v>35</v>
-      </c>
+      <c r="H57" s="54">
+        <v>879633.26716047991</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="43"/>
       <c r="B58" s="44"/>
       <c r="C58" s="44"/>
       <c r="D58" s="44"/>
@@ -1722,7 +1728,7 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="43" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="B59" s="44"/>
       <c r="C59" s="44"/>
@@ -1730,111 +1736,123 @@
       <c r="E59" s="44"/>
       <c r="F59" s="44"/>
       <c r="G59" s="44"/>
-      <c r="H59" s="45">
-        <f>-(H38+H52)</f>
-        <v>-795396.65</v>
-      </c>
-      <c r="J59" s="15"/>
-    </row>
-    <row r="60" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A60" s="46" t="s">
+      <c r="H59" s="49"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="B60" s="44"/>
+      <c r="C60" s="44"/>
+      <c r="D60" s="44"/>
+      <c r="E60" s="44"/>
+      <c r="F60" s="44"/>
+      <c r="G60" s="44"/>
+      <c r="H60" s="45">
+        <f>-(H39+H53)</f>
+        <v>-813896.65</v>
+      </c>
+      <c r="J60" s="15"/>
+    </row>
+    <row r="61" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="A61" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B60" s="47"/>
-      <c r="C60" s="47"/>
-      <c r="D60" s="47"/>
-      <c r="E60" s="47"/>
-      <c r="F60" s="47"/>
-      <c r="G60" s="47"/>
-      <c r="H60" s="58">
-        <f>SUM(H55:H59)</f>
-        <v>595955.21716047998</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B62" s="72" t="s">
+      <c r="B61" s="47"/>
+      <c r="C61" s="47"/>
+      <c r="D61" s="47"/>
+      <c r="E61" s="47"/>
+      <c r="F61" s="47"/>
+      <c r="G61" s="47"/>
+      <c r="H61" s="58">
+        <f>SUM(H56:H60)</f>
+        <v>577455.21716047998</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B63" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="C62" s="72"/>
-      <c r="D62" s="72"/>
-      <c r="E62" s="72"/>
-      <c r="F62" s="72"/>
-      <c r="G62" s="72"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B63" s="72"/>
-      <c r="C63" s="72"/>
-      <c r="D63" s="72"/>
-      <c r="E63" s="72"/>
-      <c r="F63" s="72"/>
-      <c r="G63" s="72"/>
+      <c r="C63" s="74"/>
+      <c r="D63" s="74"/>
+      <c r="E63" s="74"/>
+      <c r="F63" s="74"/>
+      <c r="G63" s="74"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B64" s="72"/>
-      <c r="C64" s="72"/>
-      <c r="D64" s="72"/>
-      <c r="E64" s="72"/>
-      <c r="F64" s="72"/>
-      <c r="G64" s="72"/>
+      <c r="B64" s="74"/>
+      <c r="C64" s="74"/>
+      <c r="D64" s="74"/>
+      <c r="E64" s="74"/>
+      <c r="F64" s="74"/>
+      <c r="G64" s="74"/>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B65" s="72"/>
-      <c r="C65" s="72"/>
-      <c r="D65" s="72"/>
-      <c r="E65" s="72"/>
-      <c r="F65" s="72"/>
-      <c r="G65" s="72"/>
+      <c r="B65" s="74"/>
+      <c r="C65" s="74"/>
+      <c r="D65" s="74"/>
+      <c r="E65" s="74"/>
+      <c r="F65" s="74"/>
+      <c r="G65" s="74"/>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B66" s="72"/>
-      <c r="C66" s="72"/>
-      <c r="D66" s="72"/>
-      <c r="E66" s="72"/>
-      <c r="F66" s="72"/>
-      <c r="G66" s="72"/>
+      <c r="B66" s="74"/>
+      <c r="C66" s="74"/>
+      <c r="D66" s="74"/>
+      <c r="E66" s="74"/>
+      <c r="F66" s="74"/>
+      <c r="G66" s="74"/>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B67" s="72"/>
-      <c r="C67" s="72"/>
-      <c r="D67" s="72"/>
-      <c r="E67" s="72"/>
-      <c r="F67" s="72"/>
-      <c r="G67" s="72"/>
+      <c r="B67" s="74"/>
+      <c r="C67" s="74"/>
+      <c r="D67" s="74"/>
+      <c r="E67" s="74"/>
+      <c r="F67" s="74"/>
+      <c r="G67" s="74"/>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B68" s="72"/>
-      <c r="C68" s="72"/>
-      <c r="D68" s="72"/>
-      <c r="E68" s="72"/>
-      <c r="F68" s="72"/>
-      <c r="G68" s="72"/>
+      <c r="B68" s="74"/>
+      <c r="C68" s="74"/>
+      <c r="D68" s="74"/>
+      <c r="E68" s="74"/>
+      <c r="F68" s="74"/>
+      <c r="G68" s="74"/>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B69" s="72"/>
-      <c r="C69" s="72"/>
-      <c r="D69" s="72"/>
-      <c r="E69" s="72"/>
-      <c r="F69" s="72"/>
-      <c r="G69" s="72"/>
+      <c r="B69" s="74"/>
+      <c r="C69" s="74"/>
+      <c r="D69" s="74"/>
+      <c r="E69" s="74"/>
+      <c r="F69" s="74"/>
+      <c r="G69" s="74"/>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B70" s="74"/>
+      <c r="C70" s="74"/>
+      <c r="D70" s="74"/>
+      <c r="E70" s="74"/>
+      <c r="F70" s="74"/>
+      <c r="G70" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="B62:G69"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="B63:G70"/>
     <mergeCell ref="E3:F3"/>
-    <mergeCell ref="A40:H41"/>
-    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A41:H42"/>
+    <mergeCell ref="A55:H55"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A46:G46"/>
     <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A50:G50"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/RAMON FRANCO/Mayo/GASTOS_RAMON FRANCO_MAYO.xlsx
+++ b/RAMON FRANCO/Mayo/GASTOS_RAMON FRANCO_MAYO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\RAMON FRANCO\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA11FFD6-574A-487D-8B59-665CA2E75486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F13A65D5-7754-4CB9-A35F-56E51CA6B6A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -147,9 +147,6 @@
     <t>NOS QUEDAN RECUPERAR EN CONCEPTO DE EDESUR MAL COBRADO ESTA CANTIDAD DE PLATA, HAY QUE "inventar un gasto"</t>
   </si>
   <si>
-    <t xml:space="preserve">JPL Articulos de limpieza </t>
-  </si>
-  <si>
     <t xml:space="preserve">Prevision ordinaria </t>
   </si>
   <si>
@@ -159,12 +156,6 @@
     <t>son 74897$ que recuperamos con el abono de ascensores</t>
   </si>
   <si>
-    <t>Doartero - tapa nueva tanque de agua - fabricacion y colocacion</t>
-  </si>
-  <si>
-    <t>Prevision Extraordinaria arreglo sala de ascensores</t>
-  </si>
-  <si>
     <t>TSG MAYO</t>
   </si>
   <si>
@@ -174,9 +165,6 @@
     <t>Administraciòn MAYO 2025:</t>
   </si>
   <si>
-    <t>SEÑORES PROPIETARIOS E INQUILINOS: A PARTIR DE LA LIQUIDACION DE MAYO, QUIEN NO ABONE EDESUR PAGARA CON PUNITORIOS AL MES SIGUIENTE. LA CAJA MOSTRADA NO ES LA REAL DEBIDO A QUE DENTRO DE LA MISMA SE SOSTIENEN LOS DEUDORES DE EDESUR Y NO SE PUEDEN AVANZAR EN MEJORAS.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ingreso pago por expensas - abril - </t>
   </si>
   <si>
@@ -187,6 +175,18 @@
   </si>
   <si>
     <t>Salvatierra Matias - Desobstruccion 3B</t>
+  </si>
+  <si>
+    <t>Arreglo sala de ascensores - Colocacion de ventana</t>
+  </si>
+  <si>
+    <t>Prevision Extraordinaria</t>
+  </si>
+  <si>
+    <t>Doartero -  Reparacion de puerta principal</t>
+  </si>
+  <si>
+    <t>SEÑORES PROPIETARIOS E INQUILINOS: A PARTIR DE DE MAYO, QUIEN NO ABONE EDESUR PAGARA CON PUNITORIOS AL MES SIGUIENTE. LA CAJA MOSTRADA NO ES LA REAL DEBIDO A QUE DENTRO DE LA MISMA SE SOSTIENEN LOS DEUDORES DE EDESUR Y NO SE PUEDEN AVANZAR EN MEJORAS.</t>
   </si>
 </sst>
 </file>
@@ -194,9 +194,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -485,10 +485,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -504,36 +504,36 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="6" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="7" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="9" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="8" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -542,34 +542,34 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="10" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="44" fontId="12" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="6" fontId="8" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="7" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="8" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="8" fontId="10" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="6" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -581,10 +581,8 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="12" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -669,7 +667,6 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="12" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -1008,16 +1005,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L70"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1027,7 +1024,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="D2" s="13" t="s">
         <v>0</v>
@@ -1037,18 +1034,18 @@
       </c>
       <c r="H2" s="6"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="D3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="75">
+      <c r="E3" s="73">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="75"/>
+      <c r="F3" s="73"/>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="D4" s="13" t="s">
         <v>2</v>
@@ -1058,18 +1055,18 @@
       </c>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="D5" s="50" t="s">
         <v>34</v>
       </c>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="H6" s="6"/>
     </row>
-    <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>3</v>
       </c>
@@ -1077,13 +1074,13 @@
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F7" s="10"/>
       <c r="G7" s="11"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1093,7 +1090,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>4</v>
       </c>
@@ -1102,7 +1099,7 @@
       </c>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>6</v>
       </c>
@@ -1111,7 +1108,7 @@
       </c>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1121,19 +1118,19 @@
       <c r="G11" s="2"/>
       <c r="H11" s="8"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="85" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="85"/>
-      <c r="C12" s="85"/>
-      <c r="D12" s="85"/>
-      <c r="E12" s="85"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="85"/>
-      <c r="H12" s="85"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="83"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="18"/>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -1143,7 +1140,7 @@
       <c r="G13" s="19"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
         <v>28</v>
       </c>
@@ -1156,10 +1153,11 @@
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
       <c r="H14" s="63">
-        <v>253420</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+        <f>253420*5%+253420</f>
+        <v>266091</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>31</v>
       </c>
@@ -1171,11 +1169,11 @@
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
-      <c r="H15" s="71">
+      <c r="H15" s="63">
         <v>8379</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="18"/>
       <c r="B16" s="19"/>
       <c r="C16" s="18"/>
@@ -1185,7 +1183,7 @@
       <c r="G16" s="19"/>
       <c r="H16" s="63"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
         <v>7</v>
       </c>
@@ -1197,10 +1195,10 @@
       <c r="G17" s="22"/>
       <c r="H17" s="51">
         <f>SUM(H13:H16)</f>
-        <v>261799</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+        <v>274470</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="23"/>
       <c r="B18" s="24"/>
       <c r="C18" s="24"/>
@@ -1210,19 +1208,19 @@
       <c r="G18" s="24"/>
       <c r="H18" s="52"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="86" t="s">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="87"/>
-      <c r="C19" s="87"/>
-      <c r="D19" s="87"/>
-      <c r="E19" s="87"/>
-      <c r="F19" s="87"/>
-      <c r="G19" s="87"/>
-      <c r="H19" s="88"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B19" s="85"/>
+      <c r="C19" s="85"/>
+      <c r="D19" s="85"/>
+      <c r="E19" s="85"/>
+      <c r="F19" s="85"/>
+      <c r="G19" s="85"/>
+      <c r="H19" s="86"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
         <v>27</v>
       </c>
@@ -1232,11 +1230,11 @@
       <c r="E20" s="19"/>
       <c r="F20" s="19"/>
       <c r="G20" s="19"/>
-      <c r="H20" s="70">
+      <c r="H20" s="30">
         <v>24151.63</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18"/>
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
@@ -1246,7 +1244,7 @@
       <c r="G21" s="19"/>
       <c r="H21" s="26"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
         <v>9</v>
       </c>
@@ -1261,19 +1259,19 @@
         <v>24151.63</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="86" t="s">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="87"/>
-      <c r="C23" s="87"/>
-      <c r="D23" s="87"/>
-      <c r="E23" s="87"/>
-      <c r="F23" s="87"/>
-      <c r="G23" s="87"/>
-      <c r="H23" s="88"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B23" s="85"/>
+      <c r="C23" s="85"/>
+      <c r="D23" s="85"/>
+      <c r="E23" s="85"/>
+      <c r="F23" s="85"/>
+      <c r="G23" s="85"/>
+      <c r="H23" s="86"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
         <v>19</v>
       </c>
@@ -1285,9 +1283,9 @@
       <c r="G24" s="29"/>
       <c r="H24" s="30"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B25" s="19"/>
       <c r="C25" s="19"/>
@@ -1297,7 +1295,7 @@
       <c r="G25" s="19"/>
       <c r="H25" s="26"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
         <v>7</v>
       </c>
@@ -1312,21 +1310,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="89" t="s">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="89"/>
-      <c r="C27" s="89"/>
-      <c r="D27" s="89"/>
-      <c r="E27" s="89"/>
-      <c r="F27" s="89"/>
-      <c r="G27" s="89"/>
-      <c r="H27" s="89"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B27" s="87"/>
+      <c r="C27" s="87"/>
+      <c r="D27" s="87"/>
+      <c r="E27" s="87"/>
+      <c r="F27" s="87"/>
+      <c r="G27" s="87"/>
+      <c r="H27" s="87"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="19"/>
@@ -1338,9 +1336,9 @@
         <v>91930.94</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B29" s="19"/>
       <c r="C29" s="25"/>
@@ -1349,15 +1347,15 @@
       <c r="F29" s="19"/>
       <c r="G29" s="19"/>
       <c r="H29" s="26">
-        <v>40800</v>
+        <v>18500</v>
       </c>
       <c r="K29">
         <v>89897</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B30" s="19"/>
       <c r="C30" s="25"/>
@@ -1365,29 +1363,25 @@
       <c r="E30" s="59"/>
       <c r="F30" s="19"/>
       <c r="G30" s="19"/>
-      <c r="H30" s="100">
-        <v>18500</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="72" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="73"/>
-      <c r="C31" s="73"/>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="73"/>
-      <c r="G31" s="73"/>
-      <c r="H31" s="26">
-        <v>195000</v>
-      </c>
+      <c r="H30" s="26">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="70"/>
+      <c r="B31" s="71"/>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="26"/>
       <c r="K31" s="53"/>
       <c r="L31" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="21" t="s">
         <v>10</v>
       </c>
@@ -1399,25 +1393,25 @@
       <c r="G32" s="22"/>
       <c r="H32" s="27">
         <f>SUM(H28:H31)</f>
-        <v>346230.94</v>
+        <v>220430.94</v>
       </c>
       <c r="L32" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="86" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="87"/>
-      <c r="C33" s="87"/>
-      <c r="D33" s="87"/>
-      <c r="E33" s="87"/>
-      <c r="F33" s="87"/>
-      <c r="G33" s="87"/>
-      <c r="H33" s="88"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B33" s="85"/>
+      <c r="C33" s="85"/>
+      <c r="D33" s="85"/>
+      <c r="E33" s="85"/>
+      <c r="F33" s="85"/>
+      <c r="G33" s="85"/>
+      <c r="H33" s="86"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
         <v>11</v>
       </c>
@@ -1432,9 +1426,9 @@
       <c r="H34" s="31"/>
       <c r="I34" s="53"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="21" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B35" s="22"/>
       <c r="C35" s="22"/>
@@ -1447,10 +1441,10 @@
       </c>
       <c r="I35" s="53"/>
       <c r="K35" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="18"/>
       <c r="B36" s="19"/>
       <c r="C36" s="19"/>
@@ -1460,19 +1454,19 @@
       <c r="G36" s="19"/>
       <c r="H36" s="32"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="86" t="s">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="87"/>
-      <c r="C37" s="87"/>
-      <c r="D37" s="87"/>
-      <c r="E37" s="87"/>
-      <c r="F37" s="87"/>
-      <c r="G37" s="87"/>
-      <c r="H37" s="88"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B37" s="85"/>
+      <c r="C37" s="85"/>
+      <c r="D37" s="85"/>
+      <c r="E37" s="85"/>
+      <c r="F37" s="85"/>
+      <c r="G37" s="85"/>
+      <c r="H37" s="86"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="60" t="s">
         <v>36</v>
       </c>
@@ -1486,7 +1480,7 @@
         <v>47532.32</v>
       </c>
     </row>
-    <row r="39" spans="1:11" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="33" t="s">
         <v>23</v>
       </c>
@@ -1498,13 +1492,13 @@
       <c r="G39" s="34"/>
       <c r="H39" s="35">
         <f>H17+H22+H26+H32+H35+H38</f>
-        <v>813896.65</v>
+        <v>700767.65</v>
       </c>
       <c r="I39" s="62"/>
     </row>
-    <row r="40" spans="1:11" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" s="14" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A40" s="55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="56"/>
       <c r="C40" s="56"/>
@@ -1514,74 +1508,78 @@
       <c r="G40" s="56"/>
       <c r="H40" s="57"/>
     </row>
-    <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="76" t="s">
+    <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="B41" s="77"/>
-      <c r="C41" s="77"/>
-      <c r="D41" s="77"/>
-      <c r="E41" s="77"/>
-      <c r="F41" s="77"/>
-      <c r="G41" s="77"/>
-      <c r="H41" s="78"/>
-    </row>
-    <row r="42" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="79"/>
-      <c r="B42" s="80"/>
-      <c r="C42" s="80"/>
-      <c r="D42" s="80"/>
-      <c r="E42" s="80"/>
-      <c r="F42" s="80"/>
-      <c r="G42" s="80"/>
-      <c r="H42" s="81"/>
-    </row>
-    <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="90"/>
-      <c r="B43" s="91"/>
-      <c r="C43" s="91"/>
-      <c r="D43" s="91"/>
-      <c r="E43" s="91"/>
-      <c r="F43" s="91"/>
-      <c r="G43" s="92"/>
-      <c r="H43" s="36"/>
-    </row>
-    <row r="44" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="90"/>
-      <c r="B44" s="91"/>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
-      <c r="F44" s="91"/>
-      <c r="G44" s="92"/>
+      <c r="B41" s="75"/>
+      <c r="C41" s="75"/>
+      <c r="D41" s="75"/>
+      <c r="E41" s="75"/>
+      <c r="F41" s="75"/>
+      <c r="G41" s="75"/>
+      <c r="H41" s="76"/>
+    </row>
+    <row r="42" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="77"/>
+      <c r="B42" s="78"/>
+      <c r="C42" s="78"/>
+      <c r="D42" s="78"/>
+      <c r="E42" s="78"/>
+      <c r="F42" s="78"/>
+      <c r="G42" s="78"/>
+      <c r="H42" s="79"/>
+    </row>
+    <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="70" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="71"/>
+      <c r="C43" s="71"/>
+      <c r="D43" s="71"/>
+      <c r="E43" s="71"/>
+      <c r="F43" s="71"/>
+      <c r="G43" s="71"/>
+      <c r="H43" s="36">
+        <v>420000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="88"/>
+      <c r="B44" s="89"/>
+      <c r="C44" s="89"/>
+      <c r="D44" s="89"/>
+      <c r="E44" s="89"/>
+      <c r="F44" s="89"/>
+      <c r="G44" s="90"/>
       <c r="H44" s="36"/>
     </row>
-    <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="93"/>
-      <c r="B45" s="94"/>
-      <c r="C45" s="94"/>
-      <c r="D45" s="94"/>
-      <c r="E45" s="94"/>
-      <c r="F45" s="94"/>
-      <c r="G45" s="95"/>
+    <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="91"/>
+      <c r="B45" s="92"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
+      <c r="F45" s="92"/>
+      <c r="G45" s="93"/>
       <c r="H45" s="36"/>
     </row>
-    <row r="46" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="96" t="s">
+    <row r="46" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="94" t="s">
         <v>29</v>
       </c>
-      <c r="B46" s="97"/>
-      <c r="C46" s="97"/>
-      <c r="D46" s="97"/>
-      <c r="E46" s="97"/>
-      <c r="F46" s="97"/>
-      <c r="G46" s="98"/>
+      <c r="B46" s="95"/>
+      <c r="C46" s="95"/>
+      <c r="D46" s="95"/>
+      <c r="E46" s="95"/>
+      <c r="F46" s="95"/>
+      <c r="G46" s="96"/>
       <c r="H46" s="37">
         <f>SUM(H43:H45)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+        <v>420000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="19"/>
       <c r="B47" s="19"/>
       <c r="C47" s="19"/>
@@ -1591,9 +1589,9 @@
       <c r="G47" s="19"/>
       <c r="H47" s="19"/>
     </row>
-    <row r="48" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="65" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B48" s="66"/>
       <c r="C48" s="66"/>
@@ -1601,11 +1599,9 @@
       <c r="E48" s="66"/>
       <c r="F48" s="66"/>
       <c r="G48" s="67"/>
-      <c r="H48" s="64">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H48" s="64"/>
+    </row>
+    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="19"/>
       <c r="B49" s="19"/>
       <c r="C49" s="19"/>
@@ -1616,22 +1612,22 @@
       <c r="H49" s="19"/>
       <c r="J49" s="15"/>
     </row>
-    <row r="50" spans="1:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="99" t="s">
+    <row r="50" spans="1:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="97" t="s">
         <v>37</v>
       </c>
-      <c r="B50" s="99"/>
-      <c r="C50" s="99"/>
-      <c r="D50" s="99"/>
-      <c r="E50" s="99"/>
-      <c r="F50" s="99"/>
-      <c r="G50" s="99"/>
+      <c r="B50" s="97"/>
+      <c r="C50" s="97"/>
+      <c r="D50" s="97"/>
+      <c r="E50" s="97"/>
+      <c r="F50" s="97"/>
+      <c r="G50" s="97"/>
       <c r="H50" s="35">
         <f>+H39+H40</f>
-        <v>813896.65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+        <v>700767.65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="38"/>
       <c r="B51" s="38"/>
       <c r="C51" s="38"/>
@@ -1641,7 +1637,7 @@
       <c r="G51" s="38"/>
       <c r="H51" s="39"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="19"/>
       <c r="B52" s="19"/>
       <c r="C52" s="19"/>
@@ -1651,7 +1647,7 @@
       <c r="G52" s="19"/>
       <c r="H52" s="19"/>
     </row>
-    <row r="53" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="33" t="s">
         <v>33</v>
       </c>
@@ -1663,10 +1659,10 @@
       <c r="G53" s="34"/>
       <c r="H53" s="40">
         <f>H46</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+        <v>420000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="19"/>
       <c r="B54" s="19"/>
       <c r="C54" s="19"/>
@@ -1676,19 +1672,19 @@
       <c r="G54" s="19"/>
       <c r="H54" s="19"/>
     </row>
-    <row r="55" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A55" s="82" t="s">
+    <row r="55" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A55" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="B55" s="83"/>
-      <c r="C55" s="83"/>
-      <c r="D55" s="83"/>
-      <c r="E55" s="83"/>
-      <c r="F55" s="83"/>
-      <c r="G55" s="83"/>
-      <c r="H55" s="84"/>
-    </row>
-    <row r="56" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="B55" s="81"/>
+      <c r="C55" s="81"/>
+      <c r="D55" s="81"/>
+      <c r="E55" s="81"/>
+      <c r="F55" s="81"/>
+      <c r="G55" s="81"/>
+      <c r="H55" s="82"/>
+    </row>
+    <row r="56" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A56" s="41" t="s">
         <v>17</v>
       </c>
@@ -1699,12 +1695,12 @@
       <c r="F56" s="42"/>
       <c r="G56" s="42"/>
       <c r="H56" s="48">
-        <v>511718.6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>596709.46716047998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="43" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B57" s="44"/>
       <c r="C57" s="44"/>
@@ -1713,10 +1709,10 @@
       <c r="F57" s="44"/>
       <c r="G57" s="44"/>
       <c r="H57" s="54">
-        <v>879633.26716047991</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>995172.28472</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="43"/>
       <c r="B58" s="44"/>
       <c r="C58" s="44"/>
@@ -1726,7 +1722,7 @@
       <c r="G58" s="44"/>
       <c r="H58" s="49"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="43" t="s">
         <v>35</v>
       </c>
@@ -1738,9 +1734,9 @@
       <c r="G59" s="44"/>
       <c r="H59" s="49"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="43" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B60" s="44"/>
       <c r="C60" s="44"/>
@@ -1750,11 +1746,11 @@
       <c r="G60" s="44"/>
       <c r="H60" s="45">
         <f>-(H39+H53)</f>
-        <v>-813896.65</v>
+        <v>-1120767.6499999999</v>
       </c>
       <c r="J60" s="15"/>
     </row>
-    <row r="61" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A61" s="46" t="s">
         <v>16</v>
       </c>
@@ -1766,74 +1762,74 @@
       <c r="G61" s="47"/>
       <c r="H61" s="58">
         <f>SUM(H56:H60)</f>
-        <v>577455.21716047998</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B63" s="74" t="s">
-        <v>48</v>
-      </c>
-      <c r="C63" s="74"/>
-      <c r="D63" s="74"/>
-      <c r="E63" s="74"/>
-      <c r="F63" s="74"/>
-      <c r="G63" s="74"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B64" s="74"/>
-      <c r="C64" s="74"/>
-      <c r="D64" s="74"/>
-      <c r="E64" s="74"/>
-      <c r="F64" s="74"/>
-      <c r="G64" s="74"/>
-    </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B65" s="74"/>
-      <c r="C65" s="74"/>
-      <c r="D65" s="74"/>
-      <c r="E65" s="74"/>
-      <c r="F65" s="74"/>
-      <c r="G65" s="74"/>
-    </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B66" s="74"/>
-      <c r="C66" s="74"/>
-      <c r="D66" s="74"/>
-      <c r="E66" s="74"/>
-      <c r="F66" s="74"/>
-      <c r="G66" s="74"/>
-    </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B67" s="74"/>
-      <c r="C67" s="74"/>
-      <c r="D67" s="74"/>
-      <c r="E67" s="74"/>
-      <c r="F67" s="74"/>
-      <c r="G67" s="74"/>
-    </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B68" s="74"/>
-      <c r="C68" s="74"/>
-      <c r="D68" s="74"/>
-      <c r="E68" s="74"/>
-      <c r="F68" s="74"/>
-      <c r="G68" s="74"/>
-    </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B69" s="74"/>
-      <c r="C69" s="74"/>
-      <c r="D69" s="74"/>
-      <c r="E69" s="74"/>
-      <c r="F69" s="74"/>
-      <c r="G69" s="74"/>
-    </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B70" s="74"/>
-      <c r="C70" s="74"/>
-      <c r="D70" s="74"/>
-      <c r="E70" s="74"/>
-      <c r="F70" s="74"/>
-      <c r="G70" s="74"/>
+        <v>471114.10188048007</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B63" s="72" t="s">
+        <v>52</v>
+      </c>
+      <c r="C63" s="72"/>
+      <c r="D63" s="72"/>
+      <c r="E63" s="72"/>
+      <c r="F63" s="72"/>
+      <c r="G63" s="72"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B64" s="72"/>
+      <c r="C64" s="72"/>
+      <c r="D64" s="72"/>
+      <c r="E64" s="72"/>
+      <c r="F64" s="72"/>
+      <c r="G64" s="72"/>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B65" s="72"/>
+      <c r="C65" s="72"/>
+      <c r="D65" s="72"/>
+      <c r="E65" s="72"/>
+      <c r="F65" s="72"/>
+      <c r="G65" s="72"/>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B66" s="72"/>
+      <c r="C66" s="72"/>
+      <c r="D66" s="72"/>
+      <c r="E66" s="72"/>
+      <c r="F66" s="72"/>
+      <c r="G66" s="72"/>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B67" s="72"/>
+      <c r="C67" s="72"/>
+      <c r="D67" s="72"/>
+      <c r="E67" s="72"/>
+      <c r="F67" s="72"/>
+      <c r="G67" s="72"/>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B68" s="72"/>
+      <c r="C68" s="72"/>
+      <c r="D68" s="72"/>
+      <c r="E68" s="72"/>
+      <c r="F68" s="72"/>
+      <c r="G68" s="72"/>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B69" s="72"/>
+      <c r="C69" s="72"/>
+      <c r="D69" s="72"/>
+      <c r="E69" s="72"/>
+      <c r="F69" s="72"/>
+      <c r="G69" s="72"/>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B70" s="72"/>
+      <c r="C70" s="72"/>
+      <c r="D70" s="72"/>
+      <c r="E70" s="72"/>
+      <c r="F70" s="72"/>
+      <c r="G70" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="16">
